--- a/docs/downloads/05/tbl_agri_equip_alaotra_feramanga_atsimo.xlsx
+++ b/docs/downloads/05/tbl_agri_equip_alaotra_feramanga_atsimo.xlsx
@@ -436,12 +436,6 @@
           <t>Autres</t>
         </is>
       </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -472,12 +466,6 @@
           <t>Charrette attelée (à trac</t>
         </is>
       </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
-      <c r="D7">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -562,12 +550,6 @@
           <t>Herse/Pulvériseur/Rotovat</t>
         </is>
       </c>
-      <c r="C12">
-        <v>4</v>
-      </c>
-      <c r="D12">
-        <v>0.3</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -580,12 +562,6 @@
           <t>Motoculteur, type Kubota</t>
         </is>
       </c>
-      <c r="C13">
-        <v>2</v>
-      </c>
-      <c r="D13">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -598,12 +574,6 @@
           <t>Pioche</t>
         </is>
       </c>
-      <c r="C14">
-        <v>2</v>
-      </c>
-      <c r="D14">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -670,12 +640,6 @@
           <t>Sarcleuse</t>
         </is>
       </c>
-      <c r="C18">
-        <v>2</v>
-      </c>
-      <c r="D18">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -737,12 +701,6 @@
           <t>Autres</t>
         </is>
       </c>
-      <c r="C22">
-        <v>3</v>
-      </c>
-      <c r="D22">
-        <v>0</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -755,12 +713,6 @@
           <t>Barre à mine</t>
         </is>
       </c>
-      <c r="C23">
-        <v>3</v>
-      </c>
-      <c r="D23">
-        <v>0</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -773,12 +725,6 @@
           <t>Bicyclette</t>
         </is>
       </c>
-      <c r="C24">
-        <v>4</v>
-      </c>
-      <c r="D24">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -809,12 +755,6 @@
           <t>Brouette</t>
         </is>
       </c>
-      <c r="C26">
-        <v>2</v>
-      </c>
-      <c r="D26">
-        <v>0</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -845,12 +785,6 @@
           <t>Camion</t>
         </is>
       </c>
-      <c r="C28">
-        <v>1</v>
-      </c>
-      <c r="D28">
-        <v>0</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -863,12 +797,6 @@
           <t>Charrette attelée (à trac</t>
         </is>
       </c>
-      <c r="C29">
-        <v>3</v>
-      </c>
-      <c r="D29">
-        <v>0</v>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -881,12 +809,6 @@
           <t>Charrette non attelée (à</t>
         </is>
       </c>
-      <c r="C30">
-        <v>1</v>
-      </c>
-      <c r="D30">
-        <v>0</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -935,12 +857,6 @@
           <t>Egreneuse</t>
         </is>
       </c>
-      <c r="C33">
-        <v>3</v>
-      </c>
-      <c r="D33">
-        <v>0</v>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1133,12 +1049,6 @@
           <t>Rouleau</t>
         </is>
       </c>
-      <c r="C44">
-        <v>1</v>
-      </c>
-      <c r="D44">
-        <v>0</v>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1187,12 +1097,6 @@
           <t>Scie</t>
         </is>
       </c>
-      <c r="C47">
-        <v>4</v>
-      </c>
-      <c r="D47">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1205,12 +1109,6 @@
           <t>Semoir attelé</t>
         </is>
       </c>
-      <c r="C48">
-        <v>3</v>
-      </c>
-      <c r="D48">
-        <v>0</v>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1222,12 +1120,6 @@
         <is>
           <t>Soubique, produits de tis</t>
         </is>
-      </c>
-      <c r="C49">
-        <v>2</v>
-      </c>
-      <c r="D49">
-        <v>0</v>
       </c>
     </row>
     <row r="50">
